--- a/updated_TIR_dataset (1).xlsx
+++ b/updated_TIR_dataset (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\BH2VMHOM07\Home$\MoorthyMy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eesharaufkhawaja/Desktop/Thesis/ code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4D1D40-5D22-48D8-A789-54E66098BA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3662CC-4F66-B94B-AC4A-1092FC683839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet4" sheetId="4" r:id="rId1"/>
@@ -347,7 +347,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -380,6 +380,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="3" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -685,10 +686,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2E927D-2B36-A64A-BD68-3CFC4C9F4ED9}">
-  <dimension ref="E1:FS42"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:FS42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="F1" s="1"/>
       <c r="G1" s="2"/>
       <c r="H1" s="3"/>
@@ -860,7 +864,7 @@
       <c r="FR1" s="9"/>
       <c r="FS1" s="31"/>
     </row>
-    <row r="2" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:175" x14ac:dyDescent="0.2">
       <c r="E2" t="s">
         <v>38</v>
       </c>
@@ -1375,7 +1379,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E3" t="s">
         <v>19</v>
       </c>
@@ -1676,7 +1680,7 @@
       <c r="FR3" s="10"/>
       <c r="FS3" s="25"/>
     </row>
-    <row r="4" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E4" t="s">
         <v>20</v>
       </c>
@@ -2185,7 +2189,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E5" t="s">
         <v>35</v>
       </c>
@@ -2534,7 +2538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E6" t="s">
         <v>36</v>
       </c>
@@ -2811,7 +2815,7 @@
       <c r="FR6" s="22"/>
       <c r="FS6" s="23"/>
     </row>
-    <row r="7" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E7" t="s">
         <v>37</v>
       </c>
@@ -3198,7 +3202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="F8" s="1"/>
       <c r="G8" s="2"/>
       <c r="H8" s="3"/>
@@ -3370,7 +3374,7 @@
       <c r="FR8" s="22"/>
       <c r="FS8" s="23"/>
     </row>
-    <row r="9" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="F9" s="1"/>
       <c r="G9" s="2"/>
       <c r="H9" s="3"/>
@@ -3542,7 +3546,7 @@
       <c r="FR9" s="22"/>
       <c r="FS9" s="23"/>
     </row>
-    <row r="10" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E10" s="15">
         <v>45769</v>
       </c>
@@ -3783,7 +3787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E11" s="15">
         <v>45799</v>
       </c>
@@ -4022,7 +4026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E12" s="15">
         <v>45830</v>
       </c>
@@ -4307,7 +4311,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E13" s="15">
         <v>45860</v>
       </c>
@@ -4590,7 +4594,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:175" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="32"/>
       <c r="E14" s="15">
         <v>45891</v>
       </c>
@@ -4871,7 +4876,7 @@
       <c r="FR14" s="22"/>
       <c r="FS14" s="23"/>
     </row>
-    <row r="15" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E15" s="15">
         <v>45922</v>
       </c>
@@ -5160,7 +5165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E16" s="15">
         <v>45952</v>
       </c>
@@ -5451,7 +5456,7 @@
       <c r="FR16" s="22"/>
       <c r="FS16" s="23"/>
     </row>
-    <row r="17" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E17" s="15">
         <v>45983</v>
       </c>
@@ -5756,7 +5761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="5:175" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:175" ht="16" x14ac:dyDescent="0.2">
       <c r="E18" s="15">
         <v>46013</v>
       </c>
@@ -6071,7 +6076,7 @@
       </c>
       <c r="FS18" s="23"/>
     </row>
-    <row r="19" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E19" s="24">
         <v>44927</v>
       </c>
@@ -6450,7 +6455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E20" s="24">
         <v>44958</v>
       </c>
@@ -6811,7 +6816,7 @@
       </c>
       <c r="FS20" s="25"/>
     </row>
-    <row r="21" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E21" s="24">
         <v>44986</v>
       </c>
@@ -7178,7 +7183,7 @@
       </c>
       <c r="FS21" s="23"/>
     </row>
-    <row r="22" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E22" s="24">
         <v>45017</v>
       </c>
@@ -7549,7 +7554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E23" s="24">
         <v>45047</v>
       </c>
@@ -7910,7 +7915,7 @@
       </c>
       <c r="FS23" s="25"/>
     </row>
-    <row r="24" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E24" s="24">
         <v>45078</v>
       </c>
@@ -8273,7 +8278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E25" s="24">
         <v>45108</v>
       </c>
@@ -8616,7 +8621,7 @@
       </c>
       <c r="FS25" s="25"/>
     </row>
-    <row r="26" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E26" s="24">
         <v>45139</v>
       </c>
@@ -8973,7 +8978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E27" s="24">
         <v>45170</v>
       </c>
@@ -9340,7 +9345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E28" s="24">
         <v>45200</v>
       </c>
@@ -9703,7 +9708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="29" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E29" s="24">
         <v>45231</v>
       </c>
@@ -10082,7 +10087,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E30" s="24">
         <v>45261</v>
       </c>
@@ -10453,7 +10458,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="31" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E31" s="24">
         <v>45292</v>
       </c>
@@ -10830,7 +10835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E32" s="24">
         <v>45323</v>
       </c>
@@ -11211,7 +11216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E33" s="24">
         <v>45352</v>
       </c>
@@ -11588,7 +11593,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E34" s="24">
         <v>45383</v>
       </c>
@@ -11971,7 +11976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E35" s="24">
         <v>45413</v>
       </c>
@@ -12336,7 +12341,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E36" s="24">
         <v>45444</v>
       </c>
@@ -12713,7 +12718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E37" s="24">
         <v>45474</v>
       </c>
@@ -13088,7 +13093,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E38" s="24">
         <v>45505</v>
       </c>
@@ -13463,7 +13468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E39" s="24">
         <v>45536</v>
       </c>
@@ -13838,7 +13843,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E40" s="24">
         <v>45566</v>
       </c>
@@ -14215,7 +14220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E41" s="24">
         <v>45597</v>
       </c>
@@ -14592,7 +14597,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="5:175" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:175" x14ac:dyDescent="0.2">
       <c r="E42" s="26">
         <v>45627</v>
       </c>
@@ -14979,9 +14984,175 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A2:A34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="15">
+        <v>45799</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="15">
+        <v>45830</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" s="15">
+        <v>45860</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" s="15">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" s="15">
+        <v>45952</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" s="15">
+        <v>45983</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="15">
+        <v>46013</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" s="24">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" s="24">
+        <v>44958</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" s="24">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" s="24">
+        <v>45017</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" s="24">
+        <v>45047</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" s="24">
+        <v>45078</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="24">
+        <v>45108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="24">
+        <v>45139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="24">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="24">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="24">
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="24">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="24">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="24">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="24">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="24">
+        <v>45383</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="24">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="24">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="24">
+        <v>45474</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="24">
+        <v>45505</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="24">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="24">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="24">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="26">
+        <v>45627</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>